--- a/uat-test-plans-reduced30/G2-16474-promotions-management-within-checkout-flow.xlsx
+++ b/uat-test-plans-reduced30/G2-16474-promotions-management-within-checkout-flow.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 5 UI-testable promotion stories mapped to 10 business checks and 8 coverage rows. 3 non-UI/evaluation stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 5 UI-testable promotion stories mapped to 10 business checks and 8 coverage rows. 3 non-UI/evaluation stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=10450; payload_chars=10448; est_tokens~2612; checklist_rows=7; matrix_rows=6; exploratory_rows=3</t>
+          <t>payload_bytes=11526; payload_chars=11524; est_tokens~2881; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -831,7 +831,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-004</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -846,28 +846,27 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Customer can apply a valid promo code and see confirmation</t>
+          <t>Customer can remove an applied promo code</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>1. Enter a valid promo code in Shopping Bag and submit.
-2. Continue into Checkout to confirm persisted state.</t>
+          <t>From a basket with an active promo code, use remove action and re-check totals and labels.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Promo code applies successfully and confirmation state is visible.
-Adjusted total remains consistent after navigation to Checkout.</t>
+          <t>Promo code is removed from visible applied state.
+Totals and promotion labels revert according to base pricing rules.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
     </row>
-    <row r="5" ht="64" customHeight="1">
+    <row r="5" ht="49" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -877,32 +876,32 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Promo Code</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Customer can remove an applied promo code</t>
+          <t>Invalid promo code shows a user-facing error without breaking flow</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>From a basket with an active promo code, use remove action and re-check totals and labels.</t>
+          <t>Submit an invalid or expired code and observe cart-level behavior and messaging.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Promo code is removed from visible applied state.
-Totals and promotion labels revert according to base pricing rules.</t>
+          <t>Clear error feedback is shown to customer.
+Checkout/cart remains usable with no corrupted totals.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
     </row>
-    <row r="6" ht="49" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -912,23 +911,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Totals Consistency</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Invalid promo code shows a user-facing error without breaking flow</t>
+          <t>Promotion-adjusted totals stay consistent through Shopping Bag, Checkout, and Order Confirmation</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Submit an invalid or expired code and observe cart-level behavior and messaging.</t>
+          <t>Progress end-to-end from bag to order completion in a promoted basket and compare subtotal/discount/total amounts.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Clear error feedback is shown to customer.
-Checkout/cart remains usable with no corrupted totals.</t>
+          <t>No unexpected total drift is observed between pages.
+Order Confirmation reflects the same applied promotion outcomes as checkout.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -937,7 +936,7 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-009</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -947,23 +946,23 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Free Shipping</t>
+          <t>Cross-Brand Consistency</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Free-shipping promotions display FREE when shipping cost is zero</t>
+          <t>Core promotion behavior is consistent across both target storefronts</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Use a scenario where shipping method cost becomes zero after promotion eligibility and inspect Shopping Bag, Checkout, and confirmation pages.</t>
+          <t>Repeat critical promo-code and pricing checks on both acceptance URLs with equivalent baskets.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Shipping price displays FREE consistently when cost is zero.
-No shipping promo element is shown when no shipping method is assigned.</t>
+          <t>Critical promotion outcomes are consistent across both brands.
+No brand-specific blocker appears for core promotion flow.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -972,7 +971,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>UAT-007</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -982,23 +981,23 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Totals Consistency</t>
+          <t>Threshold and Eligibility</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Promotion-adjusted totals stay consistent through Shopping Bag, Checkout, and Order Confirmation</t>
+          <t>Minimum spend and customer-segment eligibility behaviors are user-visible and predictable</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Progress end-to-end from bag to order completion in a promoted basket and compare subtotal/discount/total amounts.</t>
+          <t>Test one basket below threshold and one above threshold, including a segment-restricted code where available.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>No unexpected total drift is observed between pages.
-Order Confirmation reflects the same applied promotion outcomes as checkout.</t>
+          <t>Eligibility state changes are reflected clearly to the user.
+Ineligible baskets do not silently apply restricted promotions.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1015,19 +1014,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -1173,7 +1172,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-006, UAT-007</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1287,7 +1286,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-003, UAT-001</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1373,58 +1372,172 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>COV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>G2-24257</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AC-Threshold-And-Segment-Eligibility</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Minimum spend and customer-segment eligibility constraints are surfaced predictably</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Story references threshold and customer-group constraints as requirements.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Jira discussion suggests backend ownership ambiguity for eligibility checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>COV-007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>G2-24255</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AC-Regional-Discount-Formatting</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Region-specific discount formatting rules for FR and CA are correctly represented</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Story describes expected color and strikethrough behavior for FR and CA time-window cases.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Story asks to confirm whether California behavior should extend to broader US scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="49" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>COV-008</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>G2-16474</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>AC-Cross-Flow-Promo-Continuity</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Promotion outcomes remain coherent from cart through checkout and order confirmation</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>UAT-007</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007, UAT-009</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Epic in-scope and acceptance statements require visible promotion continuity across core checkout journey.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Unavailable</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Story-level AC detail is uneven, so end-to-end continuity checks are anchored primarily on Epic acceptance intent.</t>
         </is>

--- a/uat-test-plans-reduced30/G2-16474-promotions-management-within-checkout-flow.xlsx
+++ b/uat-test-plans-reduced30/G2-16474-promotions-management-within-checkout-flow.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 5 UI-testable promotion stories mapped to 10 business checks and 8 coverage rows. 3 non-UI/evaluation stories are excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC coverage guardrail enforced] 5 UI-testable promotion stories mapped to 10 business checks and 8 coverage rows. 3 non-UI/evaluation stories are excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11526; payload_chars=11524; est_tokens~2881; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
+          <t>payload_bytes=11559; payload_chars=11557; est_tokens~2890; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -831,68 +831,69 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>UAT-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Cavazzuti, Matilde || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Promo Code</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Customer can apply a valid promo code and see confirmation</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter a valid promo code in Shopping Bag and submit.
+2. Continue into Checkout to confirm persisted state.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Promo code applies successfully and confirmation state is visible.
+Adjusted total remains consistent after navigation to Checkout.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>UAT-004</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Cavazzuti, Matilde || LuxExperience</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Promo Code</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Customer can remove an applied promo code</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>From a basket with an active promo code, use remove action and re-check totals and labels.</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Promo code is removed from visible applied state.
 Totals and promotion labels revert according to base pricing rules.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="49" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>UAT-005</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Cavazzuti, Matilde || LuxExperience</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Invalid promo code shows a user-facing error without breaking flow</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Submit an invalid or expired code and observe cart-level behavior and messaging.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Clear error feedback is shown to customer.
-Checkout/cart remains usable with no corrupted totals.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -1286,7 +1287,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-003, UAT-001</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1343,7 +1344,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-004, UAT-005</t>
+          <t>UAT-004</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
